--- a/outputs/daily/hr_rankings_2026-07-12.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-12.xlsx
@@ -6304,7 +6304,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>55.8</v>
+        <v>55.7</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>50</v>
       </c>
       <c r="U22" t="n">
-        <v>64.8</v>
+        <v>63.8</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -15964,7 +15964,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>50</v>
       </c>
       <c r="U57" t="n">
-        <v>54.7</v>
+        <v>53.3</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -16058,7 +16058,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -16516,7 +16516,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>50</v>
       </c>
       <c r="U59" t="n">
-        <v>62.4</v>
+        <v>60.7</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
@@ -16743,27 +16743,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>621493</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Taylor Ward</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-12T17:35:00Z</t>
+          <t>2026-07-12T20:10:00Z</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -16773,17 +16773,17 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Seth Lugo</t>
+          <t>Kevin Gausman</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>607625</t>
+          <t>592332</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -16792,7 +16792,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>50.2</v>
+        <v>50.4</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -16806,26 +16806,26 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>32.9</v>
+        <v>43.3</v>
       </c>
       <c r="Q60" t="n">
-        <v>60.9</v>
+        <v>44.4</v>
       </c>
       <c r="R60" t="n">
-        <v>32.1</v>
+        <v>22.6</v>
       </c>
       <c r="S60" t="n">
-        <v>92.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="T60" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U60" t="n">
-        <v>50.3</v>
+        <v>30.2</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
@@ -16881,134 +16881,134 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Contact streak: 9/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.5% barrel, 17.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 16.8 HR allowed</t>
         </is>
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>44.09</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>89.54</t>
+          <t>89.56</t>
         </is>
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>99.6112</t>
+          <t>100.25</t>
         </is>
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>0.4031</t>
+          <t>0.4326</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>0.1864</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr">
         <is>
-          <t>0.3428</t>
+          <t>0.3162</t>
         </is>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>68.59</t>
+          <t>73.05</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>28.02</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>32.89</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>27.89</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>0.1413</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>8.71</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>40.49</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>90.56</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="BD60" t="inlineStr">
         <is>
-          <t>0.4849</t>
+          <t>0.4077</t>
         </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
-          <t>0.2107</t>
+          <t>0.1676</t>
         </is>
       </c>
       <c r="BF60" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="BG60" t="inlineStr"/>
       <c r="BH60" t="inlineStr"/>
       <c r="BI60" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ60" t="inlineStr"/>
@@ -17019,27 +17019,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>668227</t>
+          <t>621493</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Randy Arozarena</t>
+          <t>Taylor Ward</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-12T17:40:00Z</t>
+          <t>2026-07-12T17:35:00Z</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -17049,22 +17049,22 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Ian Seymour</t>
+          <t>Seth Lugo</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>693855</t>
+          <t>607625</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L61" t="n">
@@ -17082,26 +17082,26 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>40.4</v>
+        <v>32.9</v>
       </c>
       <c r="Q61" t="n">
-        <v>35.9</v>
+        <v>60.9</v>
       </c>
       <c r="R61" t="n">
-        <v>27.6</v>
+        <v>32.1</v>
       </c>
       <c r="S61" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T61" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U61" t="n">
-        <v>74.90000000000001</v>
+        <v>50.3</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -17157,7 +17157,7 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI61" t="inlineStr">
@@ -17167,17 +17167,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.5% barrel, 17.9 HR allowed</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
@@ -17187,104 +17187,104 @@
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>8.98</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>91.37</t>
+          <t>89.54</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
         <is>
-          <t>101.1222</t>
+          <t>99.6112</t>
         </is>
       </c>
       <c r="AR61" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>0.4031</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>0.1697</t>
+          <t>0.156</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr">
         <is>
-          <t>0.3452</t>
+          <t>0.3428</t>
         </is>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>71.39</t>
+          <t>68.59</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>34.61</t>
+          <t>32.89</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>0.1733</t>
+          <t>0.1413</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>10.47</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>88.21</t>
+          <t>90.56</t>
         </is>
       </c>
       <c r="BD61" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.4849</t>
         </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
-          <t>0.1537</t>
+          <t>0.2107</t>
         </is>
       </c>
       <c r="BF61" t="inlineStr">
         <is>
-          <t>31.34</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="BG61" t="inlineStr"/>
       <c r="BH61" t="inlineStr"/>
       <c r="BI61" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ61" t="inlineStr"/>
@@ -17295,27 +17295,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>668227</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-12T20:10:00Z</t>
+          <t>2026-07-12T17:40:00Z</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -17330,17 +17330,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Kevin Gausman</t>
+          <t>Ian Seymour</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>592332</t>
+          <t>693855</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L62" t="n">
@@ -17358,26 +17358,26 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>43.3</v>
+        <v>40.4</v>
       </c>
       <c r="Q62" t="n">
-        <v>44.4</v>
+        <v>35.9</v>
       </c>
       <c r="R62" t="n">
-        <v>22.6</v>
+        <v>27.6</v>
       </c>
       <c r="S62" t="n">
         <v>95.5</v>
       </c>
       <c r="T62" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U62" t="n">
-        <v>26.4</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
@@ -17433,134 +17433,134 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 16.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>8.98</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>44.09</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>89.56</t>
+          <t>91.37</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>100.25</t>
+          <t>101.1222</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>0.4326</t>
+          <t>0.424</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>0.1864</t>
+          <t>0.1697</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr">
         <is>
-          <t>0.3162</t>
+          <t>0.3452</t>
         </is>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>73.05</t>
+          <t>71.39</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>24.62</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>34.61</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>27.89</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1733</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>8.71</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>40.49</t>
+          <t>36.61</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>88.21</t>
         </is>
       </c>
       <c r="BD62" t="inlineStr">
         <is>
-          <t>0.4077</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
-          <t>0.1676</t>
+          <t>0.1537</t>
         </is>
       </c>
       <c r="BF62" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>31.34</t>
         </is>
       </c>
       <c r="BG62" t="inlineStr"/>
       <c r="BH62" t="inlineStr"/>
       <c r="BI62" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ62" t="inlineStr"/>
@@ -18205,7 +18205,7 @@
         <v>50</v>
       </c>
       <c r="U65" t="n">
-        <v>32.5</v>
+        <v>31.4</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
@@ -18276,7 +18276,7 @@
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 1 HR</t>
+          <t>Last 7 games: 6/29, 1 HR</t>
         </is>
       </c>
       <c r="AL65" t="inlineStr">
@@ -20607,27 +20607,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>553993</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fernando Tatis</t>
+          <t>Eugenio Suarez</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-12T20:10:00Z</t>
+          <t>2026-07-12T17:40:00Z</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -20637,26 +20637,26 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Kevin Gausman</t>
+          <t>Matthew Boyd</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>592332</t>
+          <t>571510</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -20670,26 +20670,26 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>49.8</v>
+        <v>32.4</v>
       </c>
       <c r="Q74" t="n">
-        <v>44.4</v>
+        <v>50.9</v>
       </c>
       <c r="R74" t="n">
-        <v>22.6</v>
+        <v>39.3</v>
       </c>
       <c r="S74" t="n">
-        <v>88.7</v>
+        <v>71.7</v>
       </c>
       <c r="T74" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U74" t="n">
-        <v>26.4</v>
+        <v>54.7</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
@@ -20745,134 +20745,134 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL74" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 16.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 8.5 HR allowed</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>52.64</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>92.32</t>
+          <t>88.31</t>
         </is>
       </c>
       <c r="AQ74" t="inlineStr">
         <is>
-          <t>104.4219</t>
+          <t>99.3557</t>
         </is>
       </c>
       <c r="AR74" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.3489</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>0.1652</t>
+          <t>0.1561</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr">
         <is>
-          <t>0.3539</t>
+          <t>0.2752</t>
         </is>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>75.26</t>
+          <t>71.74</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>56.56</t>
+          <t>20.48</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>32.56</t>
+          <t>48.24</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>21.03</t>
+          <t>31.52</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>0.1227</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>8.71</t>
+          <t>10.33</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>40.49</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="BD74" t="inlineStr">
         <is>
-          <t>0.4077</t>
+          <t>0.4232</t>
         </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
-          <t>0.1676</t>
+          <t>0.1706</t>
         </is>
       </c>
       <c r="BF74" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>24.38</t>
         </is>
       </c>
       <c r="BG74" t="inlineStr"/>
       <c r="BH74" t="inlineStr"/>
       <c r="BI74" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ74" t="inlineStr"/>
@@ -20883,22 +20883,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>553993</t>
+          <t>678882</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Eugenio Suarez</t>
+          <t>Ceddanne Rafaela</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -20913,17 +20913,17 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Matthew Boyd</t>
+          <t>Zach Thornton</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>571510</t>
+          <t>804267</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -20946,26 +20946,26 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>32.4</v>
+        <v>21.1</v>
       </c>
       <c r="Q75" t="n">
-        <v>50.9</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="R75" t="n">
-        <v>39.3</v>
+        <v>24.8</v>
       </c>
       <c r="S75" t="n">
-        <v>71.7</v>
+        <v>95.5</v>
       </c>
       <c r="T75" t="n">
         <v>78</v>
       </c>
       <c r="U75" t="n">
-        <v>54.7</v>
+        <v>39</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
@@ -21004,7 +21004,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr"/>
@@ -21021,134 +21021,134 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 8/31, 1 HR</t>
         </is>
       </c>
       <c r="AL75" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 8.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>88.31</t>
+          <t>86.76</t>
         </is>
       </c>
       <c r="AQ75" t="inlineStr">
         <is>
-          <t>99.3557</t>
+          <t>97.7591</t>
         </is>
       </c>
       <c r="AR75" t="inlineStr">
         <is>
-          <t>0.3489</t>
+          <t>0.3733</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>0.1561</t>
+          <t>0.1292</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr">
         <is>
-          <t>0.2752</t>
+          <t>0.2938</t>
         </is>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>71.74</t>
+          <t>70.23</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>20.48</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>48.24</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>24.18</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.1573</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="BD75" t="inlineStr">
         <is>
-          <t>0.4232</t>
+          <t>0.491</t>
         </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
-          <t>0.1706</t>
+          <t>0.208</t>
         </is>
       </c>
       <c r="BF75" t="inlineStr">
         <is>
-          <t>24.38</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="BG75" t="inlineStr"/>
       <c r="BH75" t="inlineStr"/>
       <c r="BI75" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ75" t="inlineStr"/>
@@ -21159,27 +21159,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>678882</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ceddanne Rafaela</t>
+          <t>Fernando Tatis</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-12T17:40:00Z</t>
+          <t>2026-07-12T20:10:00Z</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -21189,22 +21189,22 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Zach Thornton</t>
+          <t>Kevin Gausman</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>804267</t>
+          <t>592332</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L76" t="n">
@@ -21222,26 +21222,26 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>21.1</v>
+        <v>49.8</v>
       </c>
       <c r="Q76" t="n">
-        <v>64.90000000000001</v>
+        <v>44.4</v>
       </c>
       <c r="R76" t="n">
-        <v>24.8</v>
+        <v>22.6</v>
       </c>
       <c r="S76" t="n">
-        <v>95.5</v>
+        <v>88.7</v>
       </c>
       <c r="T76" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U76" t="n">
-        <v>39</v>
+        <v>24.9</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
@@ -21280,7 +21280,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD76" t="inlineStr"/>
@@ -21302,129 +21302,129 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/31, 1 HR</t>
+          <t>Last 7 games: 8/28, 0 HR</t>
         </is>
       </c>
       <c r="AL76" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 16.8 HR allowed</t>
         </is>
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>52.64</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>86.76</t>
+          <t>92.32</t>
         </is>
       </c>
       <c r="AQ76" t="inlineStr">
         <is>
-          <t>97.7591</t>
+          <t>104.4219</t>
         </is>
       </c>
       <c r="AR76" t="inlineStr">
         <is>
-          <t>0.3733</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>0.1292</t>
+          <t>0.1652</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr">
         <is>
-          <t>0.2938</t>
+          <t>0.3539</t>
         </is>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>70.23</t>
+          <t>75.26</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>56.56</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>32.56</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>24.18</t>
+          <t>21.03</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>0.1573</t>
+          <t>0.1227</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>8.71</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>40.49</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="BD76" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>0.4077</t>
         </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>0.1676</t>
         </is>
       </c>
       <c r="BF76" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="BG76" t="inlineStr"/>
       <c r="BH76" t="inlineStr"/>
       <c r="BI76" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ76" t="inlineStr"/>
@@ -32199,27 +32199,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-07-12T20:10:00Z</t>
+          <t>2026-07-12T16:15:00Z</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -32229,26 +32229,26 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Mitch Bratt</t>
+          <t>Paul Skenes</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>683352</t>
+          <t>694973</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>44.5</v>
+        <v>44.4</v>
       </c>
       <c r="M116" t="inlineStr">
         <is>
@@ -32266,22 +32266,22 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>38.9</v>
+        <v>39.2</v>
       </c>
       <c r="Q116" t="n">
-        <v>19.8</v>
+        <v>24.8</v>
       </c>
       <c r="R116" t="n">
-        <v>27.6</v>
+        <v>24.3</v>
       </c>
       <c r="S116" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T116" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U116" t="n">
-        <v>48.1</v>
+        <v>35.3</v>
       </c>
       <c r="V116" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y116" t="inlineStr">
@@ -32320,7 +32320,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD116" t="inlineStr"/>
@@ -32342,7 +32342,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
@@ -32352,12 +32352,12 @@
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/22, 1 HR</t>
+          <t>Last 7 games: 7/30, 1 HR</t>
         </is>
       </c>
       <c r="AL116" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM116" t="inlineStr">
@@ -32367,104 +32367,104 @@
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>42.03</t>
+          <t>45.16</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>90.96</t>
         </is>
       </c>
       <c r="AQ116" t="inlineStr">
         <is>
-          <t>100.1211</t>
+          <t>100.7153</t>
         </is>
       </c>
       <c r="AR116" t="inlineStr">
         <is>
-          <t>0.4448</t>
+          <t>0.4381</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
         <is>
-          <t>0.1791</t>
+          <t>0.1796</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr">
         <is>
-          <t>0.3342</t>
+          <t>0.3427</t>
         </is>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>72.88</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>12.22</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>29.42</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>0.2002</t>
+          <t>0.1792</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.81</t>
         </is>
       </c>
       <c r="BD116" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>0.321</t>
         </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="BF116" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.06</t>
         </is>
       </c>
       <c r="BG116" t="inlineStr"/>
       <c r="BH116" t="inlineStr"/>
       <c r="BI116" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ116" t="inlineStr"/>
@@ -32475,27 +32475,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-07-12T16:15:00Z</t>
+          <t>2026-07-12T20:10:00Z</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -32505,22 +32505,22 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>Mitch Bratt</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>694973</t>
+          <t>683352</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L117" t="n">
@@ -32542,22 +32542,22 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>39.2</v>
+        <v>38.9</v>
       </c>
       <c r="Q117" t="n">
-        <v>24.8</v>
+        <v>19.8</v>
       </c>
       <c r="R117" t="n">
-        <v>24.3</v>
+        <v>27.6</v>
       </c>
       <c r="S117" t="n">
-        <v>92.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="T117" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U117" t="n">
-        <v>35.3</v>
+        <v>46</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -32571,7 +32571,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr">
@@ -32596,7 +32596,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD117" t="inlineStr"/>
@@ -32618,7 +32618,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
@@ -32628,12 +32628,12 @@
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/30, 1 HR</t>
+          <t>Last 7 games: 7/23, 1 HR</t>
         </is>
       </c>
       <c r="AL117" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.9% barrel, 11.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
@@ -32643,104 +32643,104 @@
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>45.16</t>
+          <t>42.03</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>90.96</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>100.7153</t>
+          <t>100.1211</t>
         </is>
       </c>
       <c r="AR117" t="inlineStr">
         <is>
-          <t>0.4381</t>
+          <t>0.4448</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>0.1796</t>
+          <t>0.1791</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr">
         <is>
-          <t>0.3427</t>
+          <t>0.3342</t>
         </is>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>72.88</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>29.42</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>0.1792</t>
+          <t>0.2002</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>87.81</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="BD117" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>0.253</t>
         </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.036</t>
         </is>
       </c>
       <c r="BF117" t="inlineStr">
         <is>
-          <t>24.06</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="BG117" t="inlineStr"/>
       <c r="BH117" t="inlineStr"/>
       <c r="BI117" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ117" t="inlineStr"/>
@@ -34959,27 +34959,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>664034</t>
+          <t>657041</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ty France</t>
+          <t>Lane Thomas</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-07-12T20:10:00Z</t>
+          <t>2026-07-12T17:35:00Z</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -34989,17 +34989,17 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Kevin Gausman</t>
+          <t>Shane Baz</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>592332</t>
+          <t>669358</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -35008,7 +35008,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
@@ -35022,26 +35022,26 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P126" t="n">
-        <v>40.9</v>
+        <v>25.1</v>
       </c>
       <c r="Q126" t="n">
-        <v>44.4</v>
+        <v>42.5</v>
       </c>
       <c r="R126" t="n">
-        <v>22.6</v>
+        <v>32.1</v>
       </c>
       <c r="S126" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T126" t="n">
         <v>50</v>
       </c>
       <c r="U126" t="n">
-        <v>33.7</v>
+        <v>64.8</v>
       </c>
       <c r="V126" t="inlineStr">
         <is>
@@ -35055,7 +35055,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y126" t="inlineStr">
@@ -35097,27 +35097,27 @@
       </c>
       <c r="AH126" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL126" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 16.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM126" t="inlineStr">
@@ -35127,104 +35127,104 @@
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>45.39</t>
+          <t>38.09</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>90.69</t>
+          <t>88.64</t>
         </is>
       </c>
       <c r="AQ126" t="inlineStr">
         <is>
-          <t>101.0553</t>
+          <t>99.4115</t>
         </is>
       </c>
       <c r="AR126" t="inlineStr">
         <is>
-          <t>0.4159</t>
+          <t>0.3455</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.1208</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr">
         <is>
-          <t>0.3126</t>
+          <t>0.3011</t>
         </is>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>72.42</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>22.52</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>26.14</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>0.1807</t>
+          <t>0.1435</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>8.71</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>40.49</t>
+          <t>40.66</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>89.84</t>
         </is>
       </c>
       <c r="BD126" t="inlineStr">
         <is>
-          <t>0.4077</t>
+          <t>0.4056</t>
         </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
-          <t>0.1676</t>
+          <t>0.1539</t>
         </is>
       </c>
       <c r="BF126" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="BG126" t="inlineStr"/>
       <c r="BH126" t="inlineStr"/>
       <c r="BI126" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ126" t="inlineStr"/>
@@ -35235,27 +35235,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>657041</t>
+          <t>663616</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Lane Thomas</t>
+          <t>Trevor Larnach</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-07-12T17:35:00Z</t>
+          <t>2026-07-12T18:10:00Z</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -35265,17 +35265,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Shane Baz</t>
+          <t>José Soriano</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>669358</t>
+          <t>667755</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -35298,26 +35298,26 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P127" t="n">
-        <v>25.1</v>
+        <v>29.1</v>
       </c>
       <c r="Q127" t="n">
-        <v>42.5</v>
+        <v>36.4</v>
       </c>
       <c r="R127" t="n">
-        <v>32.1</v>
+        <v>27.1</v>
       </c>
       <c r="S127" t="n">
-        <v>90.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T127" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U127" t="n">
-        <v>64.8</v>
+        <v>34.4</v>
       </c>
       <c r="V127" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
@@ -35373,27 +35373,27 @@
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/22, 1 HR</t>
         </is>
       </c>
       <c r="AL127" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 14.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.0% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM127" t="inlineStr">
@@ -35403,104 +35403,104 @@
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>38.21</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>88.64</t>
+          <t>88.38</t>
         </is>
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>99.4115</t>
+          <t>99.3933</t>
         </is>
       </c>
       <c r="AR127" t="inlineStr">
         <is>
-          <t>0.3455</t>
+          <t>0.4016</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>0.1208</t>
+          <t>0.1418</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr">
         <is>
-          <t>0.3011</t>
+          <t>0.3327</t>
         </is>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>72.42</t>
+          <t>71.99</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>20.89</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>26.14</t>
+          <t>25.17</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>0.1435</t>
+          <t>0.154</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>40.66</t>
+          <t>40.36</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>89.84</t>
+          <t>89.23</t>
         </is>
       </c>
       <c r="BD127" t="inlineStr">
         <is>
-          <t>0.4056</t>
+          <t>0.3761</t>
         </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
-          <t>0.1539</t>
+          <t>0.1376</t>
         </is>
       </c>
       <c r="BF127" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>19.38</t>
         </is>
       </c>
       <c r="BG127" t="inlineStr"/>
       <c r="BH127" t="inlineStr"/>
       <c r="BI127" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ127" t="inlineStr"/>
@@ -35511,27 +35511,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>663616</t>
+          <t>664034</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Trevor Larnach</t>
+          <t>Ty France</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-07-12T18:10:00Z</t>
+          <t>2026-07-12T20:10:00Z</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -35541,17 +35541,17 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>José Soriano</t>
+          <t>Kevin Gausman</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>667755</t>
+          <t>592332</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -35574,26 +35574,26 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P128" t="n">
-        <v>29.1</v>
+        <v>40.9</v>
       </c>
       <c r="Q128" t="n">
-        <v>36.4</v>
+        <v>44.4</v>
       </c>
       <c r="R128" t="n">
-        <v>27.1</v>
+        <v>22.6</v>
       </c>
       <c r="S128" t="n">
-        <v>88.7</v>
+        <v>71.7</v>
       </c>
       <c r="T128" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U128" t="n">
-        <v>34.4</v>
+        <v>32.5</v>
       </c>
       <c r="V128" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y128" t="inlineStr">
@@ -35649,12 +35649,12 @@
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ128" t="inlineStr">
@@ -35664,12 +35664,12 @@
       </c>
       <c r="AK128" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/22, 1 HR</t>
+          <t>Last 7 games: 6/28, 1 HR</t>
         </is>
       </c>
       <c r="AL128" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.0% barrel, 12.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 16.8 HR allowed</t>
         </is>
       </c>
       <c r="AM128" t="inlineStr">
@@ -35679,104 +35679,104 @@
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>38.21</t>
+          <t>45.39</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>90.69</t>
         </is>
       </c>
       <c r="AQ128" t="inlineStr">
         <is>
-          <t>99.3933</t>
+          <t>101.0553</t>
         </is>
       </c>
       <c r="AR128" t="inlineStr">
         <is>
-          <t>0.4016</t>
+          <t>0.4159</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr">
         <is>
-          <t>0.1418</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr">
         <is>
-          <t>0.3327</t>
+          <t>0.3126</t>
         </is>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>71.99</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>25.17</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>0.1807</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>8.71</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>40.36</t>
+          <t>40.49</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>89.23</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="BD128" t="inlineStr">
         <is>
-          <t>0.3761</t>
+          <t>0.4077</t>
         </is>
       </c>
       <c r="BE128" t="inlineStr">
         <is>
-          <t>0.1376</t>
+          <t>0.1676</t>
         </is>
       </c>
       <c r="BF128" t="inlineStr">
         <is>
-          <t>19.38</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="BG128" t="inlineStr"/>
       <c r="BH128" t="inlineStr"/>
       <c r="BI128" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ128" t="inlineStr"/>
@@ -39375,27 +39375,27 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>694384</t>
+          <t>664770</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Nolan Schanuel</t>
+          <t>Nathan Lukes</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-07-12T18:10:00Z</t>
+          <t>2026-07-12T20:10:00Z</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -39405,17 +39405,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Taj Bradley</t>
+          <t>Germán Márquez</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>671737</t>
+          <t>608566</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -39424,7 +39424,7 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>41.9</v>
+        <v>42.1</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
@@ -39442,22 +39442,22 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>12.4</v>
+        <v>9.5</v>
       </c>
       <c r="Q142" t="n">
-        <v>49.1</v>
+        <v>58.5</v>
       </c>
       <c r="R142" t="n">
-        <v>27.1</v>
+        <v>22.6</v>
       </c>
       <c r="S142" t="n">
-        <v>92.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="T142" t="n">
         <v>80</v>
       </c>
       <c r="U142" t="n">
-        <v>37.6</v>
+        <v>19.5</v>
       </c>
       <c r="V142" t="inlineStr">
         <is>
@@ -39471,7 +39471,7 @@
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y142" t="inlineStr">
@@ -39513,12 +39513,12 @@
       </c>
       <c r="AH142" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ142" t="inlineStr">
@@ -39528,12 +39528,12 @@
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>Contact streak: 10/27 over last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL142" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.2% barrel, 14.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.8% barrel, 12.5 HR allowed</t>
         </is>
       </c>
       <c r="AM142" t="inlineStr">
@@ -39543,104 +39543,104 @@
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>30.28</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>87.29</t>
+          <t>86.85</t>
         </is>
       </c>
       <c r="AQ142" t="inlineStr">
         <is>
-          <t>96.9554</t>
+          <t>96.968</t>
         </is>
       </c>
       <c r="AR142" t="inlineStr">
         <is>
-          <t>0.3803</t>
+          <t>0.3619</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>0.1071</t>
+          <t>0.0945</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr">
         <is>
-          <t>0.3242</t>
+          <t>0.3052</t>
         </is>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>67.85</t>
+          <t>67.51</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>40.31</t>
+          <t>32.96</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>18.99</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>0.1229</t>
+          <t>0.1191</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>44.03</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>90.88</t>
+          <t>89.95</t>
         </is>
       </c>
       <c r="BD142" t="inlineStr">
         <is>
-          <t>0.3861</t>
+          <t>0.4823</t>
         </is>
       </c>
       <c r="BE142" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.2103</t>
         </is>
       </c>
       <c r="BF142" t="inlineStr">
         <is>
-          <t>30.03</t>
+          <t>32.84</t>
         </is>
       </c>
       <c r="BG142" t="inlineStr"/>
       <c r="BH142" t="inlineStr"/>
       <c r="BI142" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ142" t="inlineStr"/>
@@ -39651,27 +39651,27 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>664770</t>
+          <t>694384</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Nathan Lukes</t>
+          <t>Nolan Schanuel</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-07-12T20:10:00Z</t>
+          <t>2026-07-12T18:10:00Z</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -39681,17 +39681,17 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Germán Márquez</t>
+          <t>Taj Bradley</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>608566</t>
+          <t>671737</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -39718,22 +39718,22 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>9.5</v>
+        <v>12.4</v>
       </c>
       <c r="Q143" t="n">
-        <v>58.5</v>
+        <v>49.1</v>
       </c>
       <c r="R143" t="n">
-        <v>22.6</v>
+        <v>27.1</v>
       </c>
       <c r="S143" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T143" t="n">
         <v>80</v>
       </c>
       <c r="U143" t="n">
-        <v>14.6</v>
+        <v>37.6</v>
       </c>
       <c r="V143" t="inlineStr">
         <is>
@@ -39747,7 +39747,7 @@
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y143" t="inlineStr">
@@ -39789,12 +39789,12 @@
       </c>
       <c r="AH143" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ143" t="inlineStr">
@@ -39804,12 +39804,12 @@
       </c>
       <c r="AK143" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Contact streak: 10/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL143" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.8% barrel, 12.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 14.8 HR allowed</t>
         </is>
       </c>
       <c r="AM143" t="inlineStr">
@@ -39819,104 +39819,104 @@
       </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>30.28</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>86.85</t>
+          <t>87.29</t>
         </is>
       </c>
       <c r="AQ143" t="inlineStr">
         <is>
-          <t>96.968</t>
+          <t>96.9554</t>
         </is>
       </c>
       <c r="AR143" t="inlineStr">
         <is>
-          <t>0.3619</t>
+          <t>0.3803</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr">
         <is>
-          <t>0.0945</t>
+          <t>0.1071</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr">
         <is>
-          <t>0.3052</t>
+          <t>0.3242</t>
         </is>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>67.51</t>
+          <t>67.85</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>32.96</t>
+          <t>40.31</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>0.1191</t>
+          <t>0.1229</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.22</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>44.03</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>89.95</t>
+          <t>90.88</t>
         </is>
       </c>
       <c r="BD143" t="inlineStr">
         <is>
-          <t>0.4823</t>
+          <t>0.3861</t>
         </is>
       </c>
       <c r="BE143" t="inlineStr">
         <is>
-          <t>0.2103</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="BF143" t="inlineStr">
         <is>
-          <t>32.84</t>
+          <t>30.03</t>
         </is>
       </c>
       <c r="BG143" t="inlineStr"/>
       <c r="BH143" t="inlineStr"/>
       <c r="BI143" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ143" t="inlineStr"/>
@@ -46694,7 +46694,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ168" t="inlineStr">
@@ -46704,7 +46704,7 @@
       </c>
       <c r="AK168" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/21, 0 HR</t>
+          <t>Last 7 games: 1/22, 0 HR</t>
         </is>
       </c>
       <c r="AL168" t="inlineStr">
@@ -49912,7 +49912,7 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="M180" t="inlineStr">
         <is>
@@ -49945,7 +49945,7 @@
         <v>50</v>
       </c>
       <c r="U180" t="n">
-        <v>32</v>
+        <v>30.2</v>
       </c>
       <c r="V180" t="inlineStr">
         <is>
@@ -50006,7 +50006,7 @@
       </c>
       <c r="AI180" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ180" t="inlineStr">
@@ -50016,7 +50016,7 @@
       </c>
       <c r="AK180" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Contact streak: 9/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL180" t="inlineStr">
@@ -52672,7 +52672,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="M190" t="inlineStr">
         <is>
@@ -52705,7 +52705,7 @@
         <v>50</v>
       </c>
       <c r="U190" t="n">
-        <v>60.3</v>
+        <v>56.6</v>
       </c>
       <c r="V190" t="inlineStr">
         <is>
@@ -52766,7 +52766,7 @@
       </c>
       <c r="AI190" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ190" t="inlineStr">
@@ -52776,7 +52776,7 @@
       </c>
       <c r="AK190" t="inlineStr">
         <is>
-          <t>Contact streak: 6/15 over last 7 games</t>
+          <t>Contact streak: 6/16 over last 7 games</t>
         </is>
       </c>
       <c r="AL190" t="inlineStr">
@@ -57039,27 +57039,27 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>687221</t>
+          <t>693304</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Dalton Rushing</t>
+          <t>Nick Gonzales</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-07-12T20:10:00Z</t>
+          <t>2026-07-12T16:15:00Z</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -57069,17 +57069,17 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Mitch Bratt</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>683352</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -57088,7 +57088,7 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="M206" t="inlineStr">
         <is>
@@ -57102,26 +57102,26 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P206" t="n">
-        <v>45.3</v>
+        <v>16.2</v>
       </c>
       <c r="Q206" t="n">
-        <v>19.8</v>
+        <v>32.7</v>
       </c>
       <c r="R206" t="n">
-        <v>27.6</v>
+        <v>24.3</v>
       </c>
       <c r="S206" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T206" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U206" t="n">
-        <v>12</v>
+        <v>34.2</v>
       </c>
       <c r="V206" t="inlineStr">
         <is>
@@ -57135,7 +57135,7 @@
       </c>
       <c r="X206" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y206" t="inlineStr">
@@ -57155,12 +57155,12 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>lineup projected / unconfirmed; order MLB 6 vs RotoWire 1</t>
         </is>
       </c>
       <c r="AC206" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD206" t="inlineStr"/>
@@ -57177,12 +57177,12 @@
       </c>
       <c r="AH206" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI206" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ206" t="inlineStr">
@@ -57192,12 +57192,12 @@
       </c>
       <c r="AK206" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/20, 0 HR</t>
+          <t>Contact streak: 8/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL206" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.8% barrel, 5.9 HR allowed</t>
         </is>
       </c>
       <c r="AM206" t="inlineStr">
@@ -57207,104 +57207,104 @@
       </c>
       <c r="AN206" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>44.46</t>
+          <t>37.47</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>89.82</t>
+          <t>86.91</t>
         </is>
       </c>
       <c r="AQ206" t="inlineStr">
         <is>
-          <t>101.812</t>
+          <t>98.5422</t>
         </is>
       </c>
       <c r="AR206" t="inlineStr">
         <is>
-          <t>0.4147</t>
+          <t>0.382</t>
         </is>
       </c>
       <c r="AS206" t="inlineStr">
         <is>
-          <t>0.1774</t>
+          <t>0.1056</t>
         </is>
       </c>
       <c r="AT206" t="inlineStr">
         <is>
-          <t>0.3222</t>
+          <t>0.3183</t>
         </is>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>72.61</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>12.31</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>48.24</t>
+          <t>40.51</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>27.62</t>
+          <t>20.14</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>0.1935</t>
+          <t>0.0887</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>34.04</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>88.13</t>
         </is>
       </c>
       <c r="BD206" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>0.3694</t>
         </is>
       </c>
       <c r="BE206" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>0.1593</t>
         </is>
       </c>
       <c r="BF206" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="BG206" t="inlineStr"/>
       <c r="BH206" t="inlineStr"/>
       <c r="BI206" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ206" t="inlineStr"/>
@@ -57315,27 +57315,27 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>693304</t>
+          <t>695731</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Nick Gonzales</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-07-12T16:15:00Z</t>
+          <t>2026-07-12T18:10:00Z</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -57350,17 +57350,17 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>J.T. Ginn</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>669372</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L207" t="n">
@@ -57382,22 +57382,22 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>16.2</v>
+        <v>21.2</v>
       </c>
       <c r="Q207" t="n">
-        <v>32.7</v>
+        <v>30.9</v>
       </c>
       <c r="R207" t="n">
-        <v>24.3</v>
+        <v>27.6</v>
       </c>
       <c r="S207" t="n">
         <v>71.7</v>
       </c>
       <c r="T207" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U207" t="n">
-        <v>34.2</v>
+        <v>5.1</v>
       </c>
       <c r="V207" t="inlineStr">
         <is>
@@ -57411,7 +57411,7 @@
       </c>
       <c r="X207" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y207" t="inlineStr">
@@ -57431,12 +57431,12 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed; order MLB 6 vs RotoWire 1</t>
+          <t>lineup projected / unconfirmed</t>
         </is>
       </c>
       <c r="AC207" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD207" t="inlineStr"/>
@@ -57453,12 +57453,12 @@
       </c>
       <c r="AH207" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI207" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ207" t="inlineStr">
@@ -57468,12 +57468,12 @@
       </c>
       <c r="AK207" t="inlineStr">
         <is>
-          <t>Contact streak: 8/23 over last 7 games</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL207" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.8% barrel, 5.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.5% barrel, 12.8 HR allowed</t>
         </is>
       </c>
       <c r="AM207" t="inlineStr">
@@ -57483,104 +57483,104 @@
       </c>
       <c r="AN207" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>37.47</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>86.91</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AQ207" t="inlineStr">
         <is>
-          <t>98.5422</t>
+          <t>100.3243</t>
         </is>
       </c>
       <c r="AR207" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>0.356</t>
         </is>
       </c>
       <c r="AS207" t="inlineStr">
         <is>
-          <t>0.1056</t>
+          <t>0.111</t>
         </is>
       </c>
       <c r="AT207" t="inlineStr">
         <is>
-          <t>0.3183</t>
+          <t>0.298</t>
         </is>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>0.0887</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>34.04</t>
+          <t>37.64</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>88.13</t>
+          <t>87.42</t>
         </is>
       </c>
       <c r="BD207" t="inlineStr">
         <is>
-          <t>0.3694</t>
+          <t>0.3754</t>
         </is>
       </c>
       <c r="BE207" t="inlineStr">
         <is>
-          <t>0.1593</t>
+          <t>0.1414</t>
         </is>
       </c>
       <c r="BF207" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="BG207" t="inlineStr"/>
       <c r="BH207" t="inlineStr"/>
       <c r="BI207" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ207" t="inlineStr"/>
@@ -57591,27 +57591,27 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>687221</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Dalton Rushing</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-07-12T18:10:00Z</t>
+          <t>2026-07-12T20:10:00Z</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -57621,22 +57621,22 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>J.T. Ginn</t>
+          <t>Mitch Bratt</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>669372</t>
+          <t>683352</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L208" t="n">
@@ -57654,26 +57654,26 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P208" t="n">
-        <v>21.2</v>
+        <v>45.3</v>
       </c>
       <c r="Q208" t="n">
-        <v>30.9</v>
+        <v>19.8</v>
       </c>
       <c r="R208" t="n">
         <v>27.6</v>
       </c>
       <c r="S208" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T208" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U208" t="n">
-        <v>5.1</v>
+        <v>10.6</v>
       </c>
       <c r="V208" t="inlineStr">
         <is>
@@ -57687,7 +57687,7 @@
       </c>
       <c r="X208" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y208" t="inlineStr">
@@ -57712,7 +57712,7 @@
       </c>
       <c r="AC208" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD208" t="inlineStr"/>
@@ -57734,7 +57734,7 @@
       </c>
       <c r="AI208" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ208" t="inlineStr">
@@ -57744,12 +57744,12 @@
       </c>
       <c r="AK208" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AL208" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.5% barrel, 12.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM208" t="inlineStr">
@@ -57759,104 +57759,104 @@
       </c>
       <c r="AN208" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>44.46</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.82</t>
         </is>
       </c>
       <c r="AQ208" t="inlineStr">
         <is>
-          <t>100.3243</t>
+          <t>101.812</t>
         </is>
       </c>
       <c r="AR208" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>0.4147</t>
         </is>
       </c>
       <c r="AS208" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>0.1774</t>
         </is>
       </c>
       <c r="AT208" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>0.3222</t>
         </is>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.61</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>18.03</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>48.24</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>27.62</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.1935</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>37.64</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>87.42</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="BD208" t="inlineStr">
         <is>
-          <t>0.3754</t>
+          <t>0.253</t>
         </is>
       </c>
       <c r="BE208" t="inlineStr">
         <is>
-          <t>0.1414</t>
+          <t>0.036</t>
         </is>
       </c>
       <c r="BF208" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="BG208" t="inlineStr"/>
       <c r="BH208" t="inlineStr"/>
       <c r="BI208" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ208" t="inlineStr"/>
@@ -58143,27 +58143,27 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>2026-07-12T20:10:00Z</t>
+          <t>2026-07-12T17:40:00Z</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -58173,26 +58173,26 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Mitch Bratt</t>
+          <t>Emerson Hancock</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>683352</t>
+          <t>676106</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L210" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="M210" t="inlineStr">
         <is>
@@ -58210,22 +58210,22 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>33</v>
+        <v>13.5</v>
       </c>
       <c r="Q210" t="n">
-        <v>19.8</v>
+        <v>49.8</v>
       </c>
       <c r="R210" t="n">
         <v>27.6</v>
       </c>
       <c r="S210" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T210" t="n">
         <v>50</v>
       </c>
       <c r="U210" t="n">
-        <v>22.9</v>
+        <v>39.1</v>
       </c>
       <c r="V210" t="inlineStr">
         <is>
@@ -58239,7 +58239,7 @@
       </c>
       <c r="X210" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y210" t="inlineStr">
@@ -58264,7 +58264,7 @@
       </c>
       <c r="AC210" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD210" t="inlineStr"/>
@@ -58281,12 +58281,12 @@
       </c>
       <c r="AH210" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI210" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ210" t="inlineStr">
@@ -58296,12 +58296,12 @@
       </c>
       <c r="AK210" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 0 HR</t>
+          <t>Contact streak: 8/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL210" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.0% barrel, 12.9 HR allowed</t>
         </is>
       </c>
       <c r="AM210" t="inlineStr">
@@ -58311,104 +58311,104 @@
       </c>
       <c r="AN210" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>36.86</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>89.26</t>
+          <t>88.02</t>
         </is>
       </c>
       <c r="AQ210" t="inlineStr">
         <is>
-          <t>98.9344</t>
+          <t>98.7521</t>
         </is>
       </c>
       <c r="AR210" t="inlineStr">
         <is>
-          <t>0.4151</t>
+          <t>0.3339</t>
         </is>
       </c>
       <c r="AS210" t="inlineStr">
         <is>
-          <t>0.1514</t>
+          <t>0.0852</t>
         </is>
       </c>
       <c r="AT210" t="inlineStr">
         <is>
-          <t>0.3461</t>
+          <t>0.2886</t>
         </is>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>71.51</t>
+          <t>69.63</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>44.43</t>
+          <t>27.62</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>0.1532</t>
+          <t>0.0752</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>43.27</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="BD210" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>0.4449</t>
         </is>
       </c>
       <c r="BE210" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>0.1815</t>
         </is>
       </c>
       <c r="BF210" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>28.24</t>
         </is>
       </c>
       <c r="BG210" t="inlineStr"/>
       <c r="BH210" t="inlineStr"/>
       <c r="BI210" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ210" t="inlineStr"/>
@@ -58419,27 +58419,27 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>810938</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Ben Williamson</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2026-07-12T17:40:00Z</t>
+          <t>2026-07-12T20:10:00Z</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -58449,22 +58449,22 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Emerson Hancock</t>
+          <t>Mitch Bratt</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>676106</t>
+          <t>683352</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L211" t="n">
@@ -58486,22 +58486,22 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>13.5</v>
+        <v>33</v>
       </c>
       <c r="Q211" t="n">
-        <v>49.8</v>
+        <v>19.8</v>
       </c>
       <c r="R211" t="n">
         <v>27.6</v>
       </c>
       <c r="S211" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T211" t="n">
         <v>50</v>
       </c>
       <c r="U211" t="n">
-        <v>39.1</v>
+        <v>21.1</v>
       </c>
       <c r="V211" t="inlineStr">
         <is>
@@ -58515,7 +58515,7 @@
       </c>
       <c r="X211" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y211" t="inlineStr">
@@ -58540,7 +58540,7 @@
       </c>
       <c r="AC211" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD211" t="inlineStr"/>
@@ -58557,12 +58557,12 @@
       </c>
       <c r="AH211" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI211" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ211" t="inlineStr">
@@ -58572,12 +58572,12 @@
       </c>
       <c r="AK211" t="inlineStr">
         <is>
-          <t>Contact streak: 8/21 over last 7 games</t>
+          <t>Last 7 games: 6/23, 0 HR</t>
         </is>
       </c>
       <c r="AL211" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.0% barrel, 12.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM211" t="inlineStr">
@@ -58587,104 +58587,104 @@
       </c>
       <c r="AN211" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>7.23</t>
         </is>
       </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>36.86</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>88.02</t>
+          <t>89.26</t>
         </is>
       </c>
       <c r="AQ211" t="inlineStr">
         <is>
-          <t>98.7521</t>
+          <t>98.9344</t>
         </is>
       </c>
       <c r="AR211" t="inlineStr">
         <is>
-          <t>0.3339</t>
+          <t>0.4151</t>
         </is>
       </c>
       <c r="AS211" t="inlineStr">
         <is>
-          <t>0.0852</t>
+          <t>0.1514</t>
         </is>
       </c>
       <c r="AT211" t="inlineStr">
         <is>
-          <t>0.2886</t>
+          <t>0.3461</t>
         </is>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>69.63</t>
+          <t>71.51</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>27.62</t>
+          <t>44.43</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>0.0752</t>
+          <t>0.1532</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>43.27</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="BD211" t="inlineStr">
         <is>
-          <t>0.4449</t>
+          <t>0.253</t>
         </is>
       </c>
       <c r="BE211" t="inlineStr">
         <is>
-          <t>0.1815</t>
+          <t>0.036</t>
         </is>
       </c>
       <c r="BF211" t="inlineStr">
         <is>
-          <t>28.24</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="BG211" t="inlineStr"/>
       <c r="BH211" t="inlineStr"/>
       <c r="BI211" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ211" t="inlineStr"/>
@@ -59020,7 +59020,7 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="M213" t="inlineStr">
         <is>
@@ -59053,7 +59053,7 @@
         <v>75</v>
       </c>
       <c r="U213" t="n">
-        <v>68.7</v>
+        <v>64.8</v>
       </c>
       <c r="V213" t="inlineStr">
         <is>
@@ -59114,7 +59114,7 @@
       </c>
       <c r="AI213" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ213" t="inlineStr">
@@ -66781,7 +66781,7 @@
         <v>80</v>
       </c>
       <c r="U241" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="V241" t="inlineStr">
         <is>
@@ -66842,7 +66842,7 @@
       </c>
       <c r="AI241" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ241" t="inlineStr">
@@ -66852,7 +66852,7 @@
       </c>
       <c r="AK241" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 0 HR</t>
+          <t>Last 7 games: 3/20, 0 HR</t>
         </is>
       </c>
       <c r="AL241" t="inlineStr">
@@ -67852,7 +67852,7 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="M245" t="inlineStr">
         <is>
@@ -67885,7 +67885,7 @@
         <v>75</v>
       </c>
       <c r="U245" t="n">
-        <v>26.1</v>
+        <v>23.7</v>
       </c>
       <c r="V245" t="inlineStr">
         <is>
@@ -67946,7 +67946,7 @@
       </c>
       <c r="AI245" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ245" t="inlineStr">
@@ -67956,7 +67956,7 @@
       </c>
       <c r="AK245" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/17, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL245" t="inlineStr">
